--- a/ExportOrderWebServer/Resources/ExportOrder List.xlsx
+++ b/ExportOrderWebServer/Resources/ExportOrder List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Документы\_Разработчик\_ExportOrder\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7A0AC2-6C52-4579-9D32-792FFBD29EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE1DF27-D30C-447E-B1D5-BE9601C5B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E67AD499-37B0-4D38-90A5-8F77553454F5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Consignee</t>
   </si>
@@ -57,12 +57,27 @@
   </si>
   <si>
     <t>Порт выгрузки</t>
+  </si>
+  <si>
+    <t>Vessel</t>
+  </si>
+  <si>
+    <t>Voyage</t>
+  </si>
+  <si>
+    <t>Вес, кг.</t>
+  </si>
+  <si>
+    <t>Поручений:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -107,14 +122,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,45 +479,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF03E82-E545-48A5-9D3D-21B7E717E6B3}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="1" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="70.7109375" customWidth="1"/>
+    <col min="4" max="5" width="45.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="70.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{7FF03E82-E545-48A5-9D3D-21B7E717E6B3}"/>
+  <autoFilter ref="A1:J1" xr:uid="{7FF03E82-E545-48A5-9D3D-21B7E717E6B3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>